--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2023.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2023.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1318,15 +1318,6 @@
     <t xml:space="preserve">4102</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">2104</t>
   </si>
   <si>
@@ -2065,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:49</t>
+    <t xml:space="preserve">2026-09-07 12:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2477,7 +2468,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -9020,16 +9011,16 @@
         <v>2023</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C205" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D205" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="E205" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>385</v>
@@ -9041,7 +9032,7 @@
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>63.24</v>
+        <v>62.2</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9052,16 +9043,16 @@
         <v>2023</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>385</v>
@@ -9073,7 +9064,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>62.2</v>
+        <v>61.62</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9084,16 +9075,16 @@
         <v>2023</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>385</v>
@@ -9105,7 +9096,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>61.62</v>
+        <v>60.55</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9122,10 +9113,10 @@
         <v>395</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>385</v>
@@ -9137,7 +9128,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>60.55</v>
+        <v>60.16</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9148,16 +9139,16 @@
         <v>2023</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>385</v>
@@ -9169,7 +9160,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>60.16</v>
+        <v>60</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9180,16 +9171,16 @@
         <v>2023</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>385</v>
@@ -9201,7 +9192,7 @@
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>60</v>
+        <v>59.68</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9212,16 +9203,16 @@
         <v>2023</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>385</v>
@@ -9233,7 +9224,7 @@
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>59.68</v>
+        <v>57.66</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9244,16 +9235,16 @@
         <v>2023</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>385</v>
@@ -9265,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>57.66</v>
+        <v>57.28</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9276,16 +9267,16 @@
         <v>2023</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>385</v>
@@ -9297,7 +9288,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>57.28</v>
+        <v>56.23</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9308,16 +9299,16 @@
         <v>2023</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>385</v>
@@ -9329,7 +9320,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>56.23</v>
+        <v>55.19</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9340,16 +9331,16 @@
         <v>2023</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>385</v>
@@ -9361,7 +9352,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>55.19</v>
+        <v>52.64</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9372,16 +9363,16 @@
         <v>2023</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>410</v>
+        <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>385</v>
@@ -9393,7 +9384,7 @@
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>52.64</v>
+        <v>52.37</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9410,10 +9401,10 @@
         <v>419</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>385</v>
@@ -9425,7 +9416,7 @@
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>52.37</v>
+        <v>47.13</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9436,16 +9427,16 @@
         <v>2023</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>385</v>
@@ -9457,7 +9448,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>47.13</v>
+        <v>45.34</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9468,10 +9459,10 @@
         <v>2023</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>461</v>
@@ -9480,16 +9471,16 @@
         <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>385</v>
+        <v>463</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>45.34</v>
+        <v>77.98</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9503,25 +9494,25 @@
         <v>9</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="G220" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="E220" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>77.98</v>
+        <v>74.62</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9535,25 +9526,25 @@
         <v>9</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D221" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G221" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>74.62</v>
+        <v>74.4</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9564,10 +9555,10 @@
         <v>2023</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>470</v>
@@ -9576,16 +9567,16 @@
         <v>471</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>74.4</v>
+        <v>74.12</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9599,25 +9590,25 @@
         <v>8</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="E223" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="E223" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="F223" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>74.12</v>
+        <v>74.07</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>16</v>
@@ -9628,28 +9619,28 @@
         <v>2023</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D224" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E224" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="F224" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>74.07</v>
+        <v>73.87</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>16</v>
@@ -9663,25 +9654,25 @@
         <v>9</v>
       </c>
       <c r="C225" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G225" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>73.87</v>
+        <v>71.9</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>16</v>
@@ -9695,25 +9686,25 @@
         <v>9</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F226" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D226" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G226" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>71.9</v>
+        <v>71.57</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>16</v>
@@ -9724,10 +9715,10 @@
         <v>2023</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>481</v>
@@ -9736,16 +9727,16 @@
         <v>482</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>71.57</v>
+        <v>71.16</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>16</v>
@@ -9759,25 +9750,25 @@
         <v>14</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="E228" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="E228" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="F228" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>71.16</v>
+        <v>70.93</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>16</v>
@@ -9791,19 +9782,19 @@
         <v>14</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D229" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E229" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="F229" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9820,28 +9811,28 @@
         <v>2023</v>
       </c>
       <c r="B230" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="D230" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E230" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="F230" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>70.93</v>
+        <v>70.87</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>16</v>
@@ -9855,25 +9846,25 @@
         <v>9</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G231" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>70.87</v>
+        <v>70.74</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>16</v>
@@ -9884,28 +9875,28 @@
         <v>2023</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G232" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>70.74</v>
+        <v>70.61</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>16</v>
@@ -9916,10 +9907,10 @@
         <v>2023</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>494</v>
@@ -9928,16 +9919,16 @@
         <v>495</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>70.61</v>
+        <v>70.58</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>16</v>
@@ -9948,28 +9939,28 @@
         <v>2023</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="E234" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>70.58</v>
+        <v>70.05</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>16</v>
@@ -9980,28 +9971,28 @@
         <v>2023</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="D235" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E235" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E235" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="F235" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>70.05</v>
+        <v>69.77</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>16</v>
@@ -10012,28 +10003,28 @@
         <v>2023</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D236" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="E236" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="F236" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>69.77</v>
+        <v>69.62</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>16</v>
@@ -10044,28 +10035,28 @@
         <v>2023</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G237" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>69.62</v>
+        <v>69.44</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>16</v>
@@ -10079,25 +10070,25 @@
         <v>8</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D238" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="E238" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="F238" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>69.44</v>
+        <v>69.42</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>16</v>
@@ -10108,28 +10099,28 @@
         <v>2023</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D239" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="E239" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>69.42</v>
+        <v>69.24</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>16</v>
@@ -10140,28 +10131,28 @@
         <v>2023</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D240" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="E240" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="F240" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>69.24</v>
+        <v>69.03</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>16</v>
@@ -10175,25 +10166,25 @@
         <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>512</v>
-      </c>
       <c r="F241" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>69.03</v>
+        <v>69.02</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>16</v>
@@ -10204,28 +10195,28 @@
         <v>2023</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D242" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="F242" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>69.02</v>
+        <v>67.99</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>16</v>
@@ -10236,28 +10227,28 @@
         <v>2023</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D243" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>67.99</v>
+        <v>67.98</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>16</v>
@@ -10268,28 +10259,28 @@
         <v>2023</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G244" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>67.98</v>
+        <v>67.87</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>16</v>
@@ -10303,25 +10294,25 @@
         <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>67.87</v>
+        <v>67.82</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>16</v>
@@ -10332,28 +10323,28 @@
         <v>2023</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D246" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>522</v>
-      </c>
       <c r="F246" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>67.82</v>
+        <v>67.78</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>16</v>
@@ -10364,28 +10355,28 @@
         <v>2023</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G247" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>67.78</v>
+        <v>67.56</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>16</v>
@@ -10396,28 +10387,28 @@
         <v>2023</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D248" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="F248" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>67.56</v>
+        <v>67.44</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>16</v>
@@ -10428,28 +10419,28 @@
         <v>2023</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D249" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E249" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="E249" s="2" t="s">
-        <v>528</v>
-      </c>
       <c r="F249" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>67.44</v>
+        <v>67.4</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>16</v>
@@ -10460,28 +10451,28 @@
         <v>2023</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E250" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="E250" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="F250" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>67.4</v>
+        <v>67.15</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>16</v>
@@ -10492,28 +10483,28 @@
         <v>2023</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D251" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E251" s="2" t="s">
-        <v>532</v>
-      </c>
       <c r="F251" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>67.15</v>
+        <v>67.1</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>16</v>
@@ -10524,28 +10515,28 @@
         <v>2023</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G252" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>67.1</v>
+        <v>66.98</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>16</v>
@@ -10556,28 +10547,28 @@
         <v>2023</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="F253" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>66.98</v>
+        <v>66.82</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>16</v>
@@ -10588,28 +10579,28 @@
         <v>2023</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="E254" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="F254" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>66.82</v>
+        <v>66.74</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>16</v>
@@ -10620,28 +10611,28 @@
         <v>2023</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="F255" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>66.74</v>
+        <v>66.67</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>16</v>
@@ -10652,28 +10643,28 @@
         <v>2023</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>542</v>
+        <v>493</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>66.67</v>
+        <v>66.62</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>16</v>
@@ -10684,28 +10675,28 @@
         <v>2023</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>496</v>
+        <v>542</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>66.62</v>
+        <v>66.45</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>16</v>
@@ -10716,28 +10707,28 @@
         <v>2023</v>
       </c>
       <c r="B258" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D258" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="F258" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>66.45</v>
+        <v>66.38</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>16</v>
@@ -10751,25 +10742,25 @@
         <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D259" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G259" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>66.38</v>
+        <v>66.37</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>16</v>
@@ -10780,28 +10771,28 @@
         <v>2023</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C260" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D260" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G260" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>66.37</v>
+        <v>66.15</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>16</v>
@@ -10815,25 +10806,25 @@
         <v>8</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>66.15</v>
+        <v>66.13</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>16</v>
@@ -10844,28 +10835,28 @@
         <v>2023</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D262" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E262" s="2" t="s">
-        <v>553</v>
-      </c>
       <c r="F262" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>66.13</v>
+        <v>65.77</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>16</v>
@@ -10876,28 +10867,28 @@
         <v>2023</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D263" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E263" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="E263" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="F263" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>65.77</v>
+        <v>65.37</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>16</v>
@@ -10908,28 +10899,28 @@
         <v>2023</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="D264" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="E264" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="F264" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>65.37</v>
+        <v>65.26</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>16</v>
@@ -10943,19 +10934,19 @@
         <v>8</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D265" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E265" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="E265" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="F265" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -10972,28 +10963,28 @@
         <v>2023</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>65.26</v>
+        <v>65.18</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>16</v>
@@ -11007,25 +10998,25 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D267" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G267" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>65.18</v>
+        <v>65.11</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>16</v>
@@ -11039,25 +11030,25 @@
         <v>9</v>
       </c>
       <c r="C268" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F268" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D268" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G268" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>65.11</v>
+        <v>64.65</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>16</v>
@@ -11068,28 +11059,28 @@
         <v>2023</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C269" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D269" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G269" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>64.65</v>
+        <v>64.57</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>16</v>
@@ -11100,28 +11091,28 @@
         <v>2023</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>64.57</v>
+        <v>64.56</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>16</v>
@@ -11132,28 +11123,28 @@
         <v>2023</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C271" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D271" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G271" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>64.56</v>
+        <v>64.43</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>16</v>
@@ -11167,25 +11158,25 @@
         <v>10</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>64.43</v>
+        <v>64.42</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>16</v>
@@ -11196,28 +11187,28 @@
         <v>2023</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D273" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="E273" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="F273" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>64.42</v>
+        <v>64.08</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>16</v>
@@ -11228,28 +11219,28 @@
         <v>2023</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D274" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G274" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>64.08</v>
+        <v>64.02</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>16</v>
@@ -11260,28 +11251,28 @@
         <v>2023</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D275" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E275" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>579</v>
-      </c>
       <c r="F275" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>64.02</v>
+        <v>63.68</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>16</v>
@@ -11292,28 +11283,28 @@
         <v>2023</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="D276" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="F276" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>63.68</v>
+        <v>63.59</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>16</v>
@@ -11324,28 +11315,28 @@
         <v>2023</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D277" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E277" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="F277" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>63.59</v>
+        <v>63.39</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>16</v>
@@ -11356,28 +11347,28 @@
         <v>2023</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C278" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D278" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G278" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>63.39</v>
+        <v>63.29</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>16</v>
@@ -11388,28 +11379,28 @@
         <v>2023</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D279" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>63.29</v>
+        <v>63.2</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>16</v>
@@ -11420,28 +11411,28 @@
         <v>2023</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D280" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E280" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="F280" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>63.2</v>
+        <v>63.11</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>16</v>
@@ -11452,22 +11443,22 @@
         <v>2023</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D281" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G281" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11484,28 +11475,28 @@
         <v>2023</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D282" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>593</v>
-      </c>
       <c r="F282" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>63.11</v>
+        <v>63.04</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>16</v>
@@ -11516,28 +11507,28 @@
         <v>2023</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D283" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G283" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>63.04</v>
+        <v>62.89</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>16</v>
@@ -11551,25 +11542,25 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D284" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="E284" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="F284" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>62.89</v>
+        <v>62.71</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>16</v>
@@ -11580,28 +11571,28 @@
         <v>2023</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D285" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E285" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="F285" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>62.71</v>
+        <v>62.63</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>16</v>
@@ -11615,25 +11606,25 @@
         <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D286" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G286" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>62.63</v>
+        <v>62.55</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>16</v>
@@ -11644,28 +11635,28 @@
         <v>2023</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D287" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G287" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>62.55</v>
+        <v>62.46</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>16</v>
@@ -11676,28 +11667,28 @@
         <v>2023</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D288" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>605</v>
-      </c>
       <c r="F288" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>62.46</v>
+        <v>62.38</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>16</v>
@@ -11708,28 +11699,28 @@
         <v>2023</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G289" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>62.38</v>
+        <v>62.34</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>16</v>
@@ -11740,28 +11731,28 @@
         <v>2023</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D290" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>609</v>
-      </c>
       <c r="F290" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>62.34</v>
+        <v>62.3</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>16</v>
@@ -11775,25 +11766,25 @@
         <v>10</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>62.3</v>
+        <v>62.23</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>16</v>
@@ -11804,28 +11795,28 @@
         <v>2023</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D292" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E292" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="F292" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>62.23</v>
+        <v>62.11</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>16</v>
@@ -11839,25 +11830,25 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>62.11</v>
+        <v>61.89</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>16</v>
@@ -11868,28 +11859,28 @@
         <v>2023</v>
       </c>
       <c r="B294" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D294" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E294" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="E294" s="2" t="s">
-        <v>617</v>
-      </c>
       <c r="F294" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>61.89</v>
+        <v>61.86</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>16</v>
@@ -11900,28 +11891,28 @@
         <v>2023</v>
       </c>
       <c r="B295" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>61.86</v>
+        <v>61.26</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>16</v>
@@ -11935,25 +11926,25 @@
         <v>8</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D296" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="E296" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="F296" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>61.26</v>
+        <v>61.21</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>16</v>
@@ -11964,28 +11955,28 @@
         <v>2023</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D297" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="E297" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>61.21</v>
+        <v>61.11</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>16</v>
@@ -11999,25 +11990,25 @@
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D298" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E298" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="E298" s="2" t="s">
-        <v>625</v>
-      </c>
       <c r="F298" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>61.11</v>
+        <v>61.08</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>16</v>
@@ -12031,25 +12022,25 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D299" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E299" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E299" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="F299" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>61.08</v>
+        <v>61.05</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>16</v>
@@ -12060,28 +12051,28 @@
         <v>2023</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E300" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="E300" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="F300" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>61.05</v>
+        <v>60.96</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>16</v>
@@ -12092,28 +12083,28 @@
         <v>2023</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C301" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F301" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D301" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G301" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>60.96</v>
+        <v>60.94</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>16</v>
@@ -12124,28 +12115,28 @@
         <v>2023</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>60.94</v>
+        <v>60.64</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>16</v>
@@ -12159,25 +12150,25 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="E303" s="2" t="s">
-        <v>635</v>
-      </c>
       <c r="F303" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>60.64</v>
+        <v>60.45</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>16</v>
@@ -12191,25 +12182,25 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E304" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="F304" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>60.45</v>
+        <v>60.02</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>16</v>
@@ -12220,28 +12211,28 @@
         <v>2023</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>60.02</v>
+        <v>59.74</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>16</v>
@@ -12252,28 +12243,28 @@
         <v>2023</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F306" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D306" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G306" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>59.74</v>
+        <v>59.65</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>16</v>
@@ -12284,28 +12275,28 @@
         <v>2023</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="E307" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="F307" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>59.65</v>
+        <v>59.38</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>16</v>
@@ -12316,28 +12307,28 @@
         <v>2023</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F308" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D308" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G308" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>59.38</v>
+        <v>59.24</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>16</v>
@@ -12351,25 +12342,25 @@
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E309" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="F309" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>59.24</v>
+        <v>58.61</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>16</v>
@@ -12380,28 +12371,28 @@
         <v>2023</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D310" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E310" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="E310" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="F310" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>58.61</v>
+        <v>58.58</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>16</v>
@@ -12412,28 +12403,28 @@
         <v>2023</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="F311" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D311" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G311" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>58.58</v>
+        <v>58.45</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>16</v>
@@ -12444,28 +12435,28 @@
         <v>2023</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="E312" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="F312" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>58.45</v>
+        <v>58.19</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>16</v>
@@ -12479,25 +12470,25 @@
         <v>14</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D313" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E313" s="2" t="s">
-        <v>655</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>58.19</v>
+        <v>58.16</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>16</v>
@@ -12508,28 +12499,28 @@
         <v>2023</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>657</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>58.16</v>
+        <v>57.25</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>16</v>
@@ -12540,28 +12531,28 @@
         <v>2023</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>659</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>57.25</v>
+        <v>56.86</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>16</v>
@@ -12575,25 +12566,25 @@
         <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F316" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D316" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G316" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>56.86</v>
+        <v>56.72</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>16</v>
@@ -12604,28 +12595,28 @@
         <v>2023</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C317" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="F317" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D317" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G317" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>56.72</v>
+        <v>56.12</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>16</v>
@@ -12636,28 +12627,28 @@
         <v>2023</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D318" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="E318" s="2" t="s">
-        <v>665</v>
-      </c>
       <c r="F318" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>56.12</v>
+        <v>56.03</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>16</v>
@@ -12671,25 +12662,25 @@
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E319" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="E319" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F319" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>56.03</v>
+        <v>55.43</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>16</v>
@@ -12700,28 +12691,28 @@
         <v>2023</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>55.43</v>
+        <v>54.67</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>16</v>
@@ -12732,28 +12723,28 @@
         <v>2023</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C321" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F321" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D321" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G321" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>54.67</v>
+        <v>54.26</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>16</v>
@@ -12767,25 +12758,25 @@
         <v>10</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E322" s="2" t="s">
-        <v>673</v>
-      </c>
       <c r="F322" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>54.26</v>
+        <v>53.83</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>16</v>
@@ -12796,28 +12787,28 @@
         <v>2023</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>675</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>53.83</v>
+        <v>52.21</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>16</v>
@@ -12828,67 +12819,35 @@
         <v>2023</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="D324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E324" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="E324" s="2" t="s">
-        <v>677</v>
-      </c>
       <c r="F324" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>52.21</v>
+        <v>48.94</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B325" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="D325" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="H325" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I325" s="2" t="n">
-        <v>48.94</v>
-      </c>
-      <c r="J325" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J325"/>
+  <autoFilter ref="A1:J324"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -12905,7 +12864,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12913,50 +12872,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -12978,21 +12937,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13001,7 +12960,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2023.xlsx
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:54</t>
+    <t xml:space="preserve">2026-09-08 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
